--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB913BD779C031AE933BD3190EA71D9FE0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD7D6D67-BEDE-49CD-9B9E-0FC8126ACC79}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB97B2DF2FF0DF8FC911D328CA470D9F83A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F324E533-6898-4B6F-BA4D-5F01C139A9EF}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$125</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$127</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="202">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 340 days</t>
+    <t>OverDue by 360 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -79,9 +79,6 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-07-28)</t>
-  </si>
-  <si>
     <t>Texas Instruments Taiwan</t>
   </si>
   <si>
@@ -103,7 +100,250 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 176 days</t>
+    <t>OverDue by 196 days</t>
+  </si>
+  <si>
+    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
+  </si>
+  <si>
+    <t>47270551</t>
+  </si>
+  <si>
+    <t>OverDue by 119 days</t>
+  </si>
+  <si>
+    <t>47318424</t>
+  </si>
+  <si>
+    <t>OverDue by 103 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-09-01)</t>
+  </si>
+  <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
+    <t>OverDue by 70 days</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>PO-468-061326-01</t>
+  </si>
+  <si>
+    <t>OverDue by 32 days</t>
+  </si>
+  <si>
+    <t>Tongfu Microelectronics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_NFME</t>
+  </si>
+  <si>
+    <t>OverDue by 27 days</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>17 days before Due</t>
+  </si>
+  <si>
+    <t>TI (Philippines) Inc.</t>
+  </si>
+  <si>
+    <t>4516351202_TIPI</t>
+  </si>
+  <si>
+    <t>3 days before Due</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262347</t>
+  </si>
+  <si>
+    <t>2 days before Due</t>
+  </si>
+  <si>
+    <t>3T/PO262348</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>1 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>Due Today</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC.</t>
+  </si>
+  <si>
+    <t>47369322</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>47375825</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
   </si>
   <si>
     <t>ARDENTEC CORPORATION</t>
@@ -112,271 +352,37 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 130 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-27 → 2026-05-19)</t>
-  </si>
-  <si>
-    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
-  </si>
-  <si>
-    <t>47270551</t>
-  </si>
-  <si>
-    <t>OverDue by 99 days</t>
-  </si>
-  <si>
-    <t>TI (Philippines) Inc.</t>
-  </si>
-  <si>
-    <t>4516351202_TIPI</t>
-  </si>
-  <si>
-    <t>Varies (2026-04-27 → 2026-06-25)</t>
-  </si>
-  <si>
-    <t>47318424</t>
-  </si>
-  <si>
-    <t>OverDue by 83 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-05-13 → 2026-08-25)</t>
-  </si>
-  <si>
-    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
-  </si>
-  <si>
-    <t>MO262002496</t>
-  </si>
-  <si>
-    <t>OverDue by 50 days</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>PO-468-061326-01</t>
-  </si>
-  <si>
-    <t>OverDue by 12 days</t>
-  </si>
-  <si>
-    <t>Tongfu Microelectronics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_NFME</t>
-  </si>
-  <si>
-    <t>OverDue by 7 days</t>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541541216</t>
+  </si>
+  <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
+    <t>8541563942</t>
+  </si>
+  <si>
     <t>8541571063</t>
   </si>
   <si>
-    <t>OverDue by 6 days</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>14 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>9 days before Due</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>6 days before Due</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>3T/PO262348</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>3T/PO262347</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC.</t>
-  </si>
-  <si>
-    <t>47369322</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>TBA_ADGT</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>8541541216</t>
-  </si>
-  <si>
-    <t>8541550629</t>
-  </si>
-  <si>
-    <t>8541550824</t>
-  </si>
-  <si>
-    <t>8541563942</t>
-  </si>
-  <si>
     <t>Boston Semi Equipment</t>
   </si>
   <si>
@@ -425,12 +431,6 @@
     <t>TBD_EVALUATION</t>
   </si>
   <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
     <t>4910172298</t>
   </si>
   <si>
@@ -440,15 +440,9 @@
     <t>ES072525</t>
   </si>
   <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
     <t>4516260169</t>
   </si>
   <si>
-    <t>4516446856</t>
-  </si>
-  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -632,7 +626,10 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-08-04 14:04:31</t>
+    <t>PO002810</t>
+  </si>
+  <si>
+    <t>Last updated: 2026-08-24 08:41:10</t>
   </si>
 </sst>
 </file>
@@ -977,12 +974,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1055,7 +1052,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1072,42 +1069,39 @@
         <v>355</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
       </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
       <c r="C5">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1116,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>266</v>
@@ -1128,7 +1122,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1136,25 +1130,25 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
       <c r="C6">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1163,24 +1157,24 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
       <c r="C7">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1189,220 +1183,214 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-176</v>
+        <v>-196</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46139</v>
+      </c>
+      <c r="K8">
+        <v>-119</v>
+      </c>
+      <c r="L8" t="s">
         <v>28</v>
-      </c>
-      <c r="C8">
-        <v>259</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>253</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>46108</v>
-      </c>
-      <c r="K8">
-        <v>-130</v>
-      </c>
-      <c r="L8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>21</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>19</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46155</v>
+      </c>
+      <c r="K9">
+        <v>-103</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>46139</v>
-      </c>
-      <c r="K9">
-        <v>-99</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>46188</v>
+      </c>
+      <c r="K10">
+        <v>-70</v>
+      </c>
+      <c r="L10" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>666</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>643</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>46139</v>
-      </c>
-      <c r="K10">
-        <v>-99</v>
-      </c>
-      <c r="L10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46226</v>
+      </c>
+      <c r="K11">
+        <v>-32</v>
+      </c>
+      <c r="L11" t="s">
         <v>37</v>
-      </c>
-      <c r="C11">
-        <v>35</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>15</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>46155</v>
-      </c>
-      <c r="K11">
-        <v>-83</v>
-      </c>
-      <c r="L11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <v>18</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46231</v>
+      </c>
+      <c r="K12">
+        <v>-27</v>
+      </c>
+      <c r="L12" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46188</v>
-      </c>
-      <c r="K12">
-        <v>-50</v>
-      </c>
-      <c r="L12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1411,71 +1399,71 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46226</v>
+        <v>46275</v>
       </c>
       <c r="K13">
-        <v>-12</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>694</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H14">
-        <v>29</v>
+        <v>663</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46231</v>
+        <v>46261</v>
       </c>
       <c r="K14">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1484,33 +1472,33 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="1">
-        <v>46232</v>
+        <v>46260</v>
       </c>
       <c r="K15">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1522,91 +1510,91 @@
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="K16">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C17">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>46247</v>
+        <v>46259</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C18">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>50</v>
@@ -1629,13 +1617,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1644,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1655,25 +1643,25 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1681,13 +1669,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1696,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1707,13 +1695,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1725,7 +1713,7 @@
         <v>2</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1733,10 +1721,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C24">
         <v>54</v>
@@ -1759,10 +1747,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1785,80 +1773,77 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C28">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" t="s">
-        <v>77</v>
-      </c>
       <c r="H28">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1866,10 +1851,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C29">
         <v>19</v>
@@ -1884,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H29">
         <v>19</v>
@@ -1895,10 +1880,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1913,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H30">
         <v>30</v>
@@ -1924,10 +1909,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1942,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1953,10 +1938,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1971,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1982,10 +1967,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2000,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2011,10 +1996,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2029,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2040,10 +2025,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2058,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2069,10 +2054,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2087,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2098,10 +2083,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -2116,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H37">
         <v>6</v>
@@ -2127,10 +2112,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2145,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -2156,10 +2141,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2174,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2185,10 +2170,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -2203,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -2214,10 +2199,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2232,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2243,10 +2228,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2261,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H42">
         <v>2</v>
@@ -2272,10 +2257,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2290,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2301,10 +2286,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C44">
         <v>9</v>
@@ -2319,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H44">
         <v>9</v>
@@ -2330,10 +2315,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2348,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -2359,13 +2344,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C46">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2377,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H46">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2388,13 +2373,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2406,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2417,13 +2402,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2435,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2446,10 +2431,10 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2464,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H49">
         <v>4</v>
@@ -2475,13 +2460,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2493,10 +2478,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2504,13 +2489,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2522,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H51">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2533,10 +2518,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2551,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2562,10 +2547,10 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2580,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -2591,13 +2576,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2609,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2620,13 +2605,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2638,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2649,13 +2634,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C56">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2667,10 +2652,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H56">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2678,13 +2663,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2696,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2707,10 +2692,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2725,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2736,13 +2721,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C59">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2754,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H59">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2765,13 +2750,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C60">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2783,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H60">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2794,13 +2779,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2812,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2823,13 +2808,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2841,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2852,13 +2837,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2870,10 +2855,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H63">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2881,13 +2866,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2899,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2910,13 +2895,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2928,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2939,13 +2924,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2957,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2968,13 +2953,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2986,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2997,10 +2982,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3015,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3026,13 +3011,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C69">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3044,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H69">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3055,13 +3040,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" t="s">
         <v>124</v>
       </c>
-      <c r="B70" t="s">
-        <v>126</v>
-      </c>
       <c r="C70">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3073,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H70">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3084,10 +3069,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -3102,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -3113,13 +3098,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3131,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3142,13 +3127,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3160,10 +3145,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H73">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3171,13 +3156,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3189,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3200,13 +3185,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
+        <v>126</v>
+      </c>
+      <c r="B75" t="s">
         <v>130</v>
       </c>
-      <c r="B75" t="s">
-        <v>132</v>
-      </c>
       <c r="C75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3218,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3229,13 +3214,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C76">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3247,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H76">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3258,13 +3243,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
+        <v>132</v>
+      </c>
+      <c r="B77" t="s">
         <v>133</v>
       </c>
-      <c r="B77" t="s">
-        <v>135</v>
-      </c>
       <c r="C77">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3276,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H77">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3287,13 +3272,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3305,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3316,13 +3301,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C79">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3334,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H79">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3345,13 +3330,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B80" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3363,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H80">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3374,13 +3359,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" t="s">
         <v>138</v>
       </c>
-      <c r="B81" t="s">
-        <v>141</v>
-      </c>
       <c r="C81">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3392,10 +3377,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3403,13 +3388,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3421,10 +3406,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3432,13 +3417,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3450,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3461,11 +3446,11 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
+        <v>140</v>
+      </c>
+      <c r="B84" t="s">
         <v>142</v>
       </c>
-      <c r="B84" t="s">
-        <v>145</v>
-      </c>
       <c r="C84">
         <v>1</v>
       </c>
@@ -3479,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3490,13 +3475,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3508,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3519,13 +3504,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3537,10 +3522,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3548,13 +3533,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3566,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3577,10 +3562,10 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -3595,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H88">
         <v>3</v>
@@ -3606,10 +3591,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -3624,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3635,10 +3620,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3653,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3664,13 +3649,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3682,10 +3667,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3693,13 +3678,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C92">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3711,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H92">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3722,13 +3707,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3740,10 +3725,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H93">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3751,13 +3736,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3769,10 +3754,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3780,13 +3765,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3798,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3809,13 +3794,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C96">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3827,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H96">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3838,13 +3823,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C97">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3856,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H97">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3867,13 +3852,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3885,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H98">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3896,13 +3881,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C99">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3914,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H99">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3925,13 +3910,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3943,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3954,11 +3939,11 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
+        <v>161</v>
+      </c>
+      <c r="B101" t="s">
         <v>163</v>
       </c>
-      <c r="B101" t="s">
-        <v>166</v>
-      </c>
       <c r="C101">
         <v>1</v>
       </c>
@@ -3972,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3983,10 +3968,10 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -4001,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -4012,10 +3997,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B103" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -4030,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -4041,10 +4026,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B104" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4059,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -4070,10 +4055,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4088,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -4099,10 +4084,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4117,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4128,13 +4113,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4146,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4157,13 +4142,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4175,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4186,13 +4171,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B109" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4204,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4215,10 +4200,10 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B110" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -4233,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H110">
         <v>2</v>
@@ -4244,13 +4229,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B111" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4262,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -4273,10 +4258,10 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B112" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -4291,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -4302,13 +4287,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B113" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4320,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H113">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4331,13 +4316,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B114" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4349,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4360,13 +4345,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4378,10 +4363,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4389,10 +4374,10 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B116" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4407,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H116">
         <v>2</v>
@@ -4418,13 +4403,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B117" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C117">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4436,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H117">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4447,13 +4432,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B118" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4465,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H118">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4476,13 +4461,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B119" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C119">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4494,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H119">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4505,13 +4490,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="B120" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4523,10 +4508,10 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4534,13 +4519,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B121" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C121">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4552,10 +4537,10 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H121">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4563,13 +4548,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="B122" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C122">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4581,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H122">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4592,13 +4577,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B123" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4610,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -4621,10 +4606,10 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -4639,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -4650,10 +4635,10 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B125" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -4668,12 +4653,70 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
       <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126" t="s">
+        <v>199</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>75</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" t="s">
+        <v>200</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>75</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB97B2DF2FF0DF8FC911D328CA470D9F83A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F324E533-6898-4B6F-BA4D-5F01C139A9EF}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9A08D709C2FF8E3706DF3841071D9F6B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{104F16C2-E637-4F59-909B-5D747A959244}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$127</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$129</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="207">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 360 days</t>
+    <t>OverDue by 374 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -91,7 +91,7 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-07-16)</t>
+    <t>Varies (2025-08-29 → 2026-09-10)</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
@@ -100,7 +100,10 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 196 days</t>
+    <t>OverDue by 210 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-02-09 → 2026-09-21)</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -109,16 +112,16 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 119 days</t>
+    <t>OverDue by 133 days</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 103 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-05-13 → 2026-09-01)</t>
+    <t>OverDue by 117 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-09-24)</t>
   </si>
   <si>
     <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
@@ -127,217 +130,214 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 70 days</t>
+    <t>OverDue by 84 days</t>
+  </si>
+  <si>
+    <t>Tongfu Microelectronics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_NFME</t>
+  </si>
+  <si>
+    <t>OverDue by 41 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>OverDue by 14 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>OverDue by 13 days</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262348</t>
+  </si>
+  <si>
+    <t>OverDue by 12 days</t>
+  </si>
+  <si>
+    <t>TI (Philippines) Inc.</t>
+  </si>
+  <si>
+    <t>4516351202_TIPI</t>
+  </si>
+  <si>
+    <t>OverDue by 11 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-08-27 → 2026-09-08)</t>
+  </si>
+  <si>
+    <t>47383334</t>
+  </si>
+  <si>
+    <t>18 days before Due</t>
   </si>
   <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
   </si>
   <si>
-    <t>PO-468-061326-01</t>
-  </si>
-  <si>
-    <t>OverDue by 32 days</t>
-  </si>
-  <si>
-    <t>Tongfu Microelectronics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_NFME</t>
-  </si>
-  <si>
-    <t>OverDue by 27 days</t>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>14 days before Due</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>7 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>4502615140</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
   </si>
   <si>
     <t>47301012</t>
   </si>
   <si>
-    <t>17 days before Due</t>
-  </si>
-  <si>
-    <t>TI (Philippines) Inc.</t>
-  </si>
-  <si>
-    <t>4516351202_TIPI</t>
-  </si>
-  <si>
-    <t>3 days before Due</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>3T/PO262347</t>
-  </si>
-  <si>
-    <t>2 days before Due</t>
-  </si>
-  <si>
-    <t>3T/PO262348</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>1 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>47375825</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
   </si>
   <si>
     <t>ANALOG DEVICES INC.</t>
   </si>
   <si>
     <t>47369322</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>47375825</t>
-  </si>
-  <si>
-    <t>TBA_ADGT</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
   </si>
   <si>
     <t>ANALOG DEVICES INC. CAMAS</t>
@@ -431,6 +431,12 @@
     <t>TBD_EVALUATION</t>
   </si>
   <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
     <t>4910172298</t>
   </si>
   <si>
@@ -440,9 +446,15 @@
     <t>ES072525</t>
   </si>
   <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
     <t>4516260169</t>
   </si>
   <si>
+    <t>4516446856</t>
+  </si>
+  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -485,6 +497,9 @@
     <t>3T/PO262338</t>
   </si>
   <si>
+    <t>3T/PO262347</t>
+  </si>
+  <si>
     <t>ON Semiconductor Philippines Inc</t>
   </si>
   <si>
@@ -509,9 +524,6 @@
     <t>4020007647</t>
   </si>
   <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
     <t>3030012690</t>
   </si>
   <si>
@@ -629,7 +641,10 @@
     <t>PO002810</t>
   </si>
   <si>
-    <t>Last updated: 2026-08-24 08:41:10</t>
+    <t>PO-468-061326-01</t>
+  </si>
+  <si>
+    <t>Last updated: 2026-09-07 09:47:50</t>
   </si>
 </sst>
 </file>
@@ -974,12 +989,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1052,7 +1067,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-360</v>
+        <v>-374</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1078,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-360</v>
+        <v>-374</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1110,10 +1125,10 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1122,7 +1137,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-360</v>
+        <v>-374</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1136,19 +1151,19 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1157,7 +1172,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-360</v>
+        <v>-374</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1174,39 +1189,42 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-196</v>
+        <v>-210</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
       </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -1230,33 +1248,33 @@
         <v>46139</v>
       </c>
       <c r="K8">
-        <v>-119</v>
+        <v>-133</v>
       </c>
       <c r="L8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1265,21 +1283,21 @@
         <v>46155</v>
       </c>
       <c r="K9">
-        <v>-103</v>
+        <v>-117</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1303,24 +1321,24 @@
         <v>46188</v>
       </c>
       <c r="K10">
-        <v>-70</v>
+        <v>-84</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1329,30 +1347,30 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="K11">
-        <v>-32</v>
+        <v>-41</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1364,30 +1382,30 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="I12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>46231</v>
+        <v>46258</v>
       </c>
       <c r="K12">
-        <v>-27</v>
+        <v>-14</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1399,68 +1417,68 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="K13">
-        <v>17</v>
+        <v>-13</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>694</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>663</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="L14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>694</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1469,36 +1487,39 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L15" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="M15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1510,120 +1531,129 @@
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46260</v>
+        <v>46290</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
       <c r="H17">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>46259</v>
+        <v>46286</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I19">
         <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>46279</v>
+      </c>
+      <c r="K19">
+        <v>7</v>
+      </c>
+      <c r="L19" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1632,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H20">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1643,13 +1673,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C21">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1658,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1669,13 +1699,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C22">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1684,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1695,25 +1725,25 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C23">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1721,13 +1751,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1736,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1747,13 +1777,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1762,10 +1792,13 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1773,13 +1806,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C26">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1788,24 +1821,27 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
       </c>
       <c r="H26">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1816,34 +1852,40 @@
       <c r="F27">
         <v>0</v>
       </c>
+      <c r="G27" t="s">
+        <v>72</v>
+      </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
       <c r="H28">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1851,13 +1893,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C29">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1869,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H29">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1880,13 +1922,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1898,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H30">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1909,10 +1951,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1927,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1938,10 +1980,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1956,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1967,13 +2009,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1985,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1996,13 +2038,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2014,10 +2056,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2025,10 +2067,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2043,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2054,13 +2096,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2072,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2083,13 +2125,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2101,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2112,10 +2154,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2130,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -2141,10 +2183,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2159,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2170,13 +2212,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2188,10 +2230,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2199,13 +2241,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2217,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2228,13 +2270,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2246,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2257,13 +2299,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2275,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2286,13 +2328,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2304,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H44">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2315,10 +2357,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2333,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -2344,13 +2386,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2362,10 +2404,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2373,13 +2415,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2391,10 +2433,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2402,13 +2444,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2420,10 +2462,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2431,13 +2473,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2449,10 +2491,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2460,13 +2502,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2478,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H50">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2489,13 +2531,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2507,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2518,10 +2560,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2536,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2547,13 +2589,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2565,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2576,13 +2618,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2594,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2605,10 +2647,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2623,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2634,13 +2676,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2652,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2663,13 +2705,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C57">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2681,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H57">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2692,13 +2734,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2710,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2721,13 +2763,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2739,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2750,13 +2792,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C60">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2768,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H60">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2779,13 +2821,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C61">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2797,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H61">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2808,13 +2850,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C62">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2826,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H62">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2840,10 +2882,10 @@
         <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2855,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2869,10 +2911,10 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2884,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2898,10 +2940,10 @@
         <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2913,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H65">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2924,13 +2966,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2942,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2953,10 +2995,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B67" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2971,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2982,13 +3024,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3000,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3011,10 +3053,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3029,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -3040,13 +3082,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3058,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3069,13 +3111,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3087,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3101,10 +3143,10 @@
         <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C72">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3116,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H72">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3130,10 +3172,10 @@
         <v>126</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C73">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3145,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H73">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3159,10 +3201,10 @@
         <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3174,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3185,13 +3227,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3203,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3214,13 +3256,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3232,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H76">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3243,13 +3285,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3261,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H77">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3272,13 +3314,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3290,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3301,13 +3343,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3319,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H79">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3330,13 +3372,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3348,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3359,13 +3401,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3377,10 +3419,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H81">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3388,10 +3430,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -3406,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3417,10 +3459,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C83">
         <v>3</v>
@@ -3435,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -3446,10 +3488,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -3464,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3475,10 +3517,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3493,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3504,10 +3546,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -3522,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H86">
         <v>2</v>
@@ -3533,10 +3575,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3551,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3562,10 +3604,10 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -3580,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H88">
         <v>3</v>
@@ -3591,10 +3633,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -3609,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3620,10 +3662,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3638,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3649,10 +3691,10 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3667,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -3678,10 +3720,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C92">
         <v>5</v>
@@ -3696,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -3707,10 +3749,10 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C93">
         <v>10</v>
@@ -3725,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H93">
         <v>10</v>
@@ -3736,10 +3778,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C94">
         <v>5</v>
@@ -3754,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H94">
         <v>5</v>
@@ -3765,13 +3807,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3783,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3794,13 +3836,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B96" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3812,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3823,13 +3865,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C97">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3841,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3852,13 +3894,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3870,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H98">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3881,13 +3923,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3899,10 +3941,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3910,13 +3952,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C100">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3928,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H100">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3939,13 +3981,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3957,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3968,10 +4010,10 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -3986,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3997,10 +4039,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -4015,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -4026,10 +4068,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4044,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -4055,10 +4097,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B105" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4073,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -4084,10 +4126,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4102,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4113,10 +4155,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B107" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4131,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -4142,13 +4184,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4160,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4171,13 +4213,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4189,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4200,13 +4242,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4218,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4229,10 +4271,10 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B111" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -4247,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H111">
         <v>2</v>
@@ -4258,13 +4300,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B112" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4276,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4287,10 +4329,10 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B113" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -4305,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -4316,13 +4358,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B114" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4334,10 +4376,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H114">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4345,13 +4387,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B115" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4363,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4374,13 +4416,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B116" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4392,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4403,10 +4445,10 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -4421,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H117">
         <v>2</v>
@@ -4432,13 +4474,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4450,10 +4492,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H118">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4461,13 +4503,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B119" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4479,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4490,13 +4532,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C120">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4508,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H120">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4519,13 +4561,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="B121" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4537,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4548,13 +4590,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B122" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C122">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4566,10 +4608,10 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H122">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4577,13 +4619,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="B123" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C123">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4595,10 +4637,10 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H123">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -4606,13 +4648,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B124" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -4624,10 +4666,10 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H124">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -4635,10 +4677,10 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -4653,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -4664,10 +4706,10 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B126" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -4682,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -4693,10 +4735,10 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B127" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -4711,12 +4753,70 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H127">
         <v>1</v>
       </c>
       <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A128" t="s">
+        <v>54</v>
+      </c>
+      <c r="B128" t="s">
+        <v>204</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
+        <v>72</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A129" t="s">
+        <v>54</v>
+      </c>
+      <c r="B129" t="s">
+        <v>205</v>
+      </c>
+      <c r="C129">
+        <v>5</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>72</v>
+      </c>
+      <c r="H129">
+        <v>5</v>
+      </c>
+      <c r="I129">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9A08D709C2FF8E3706DF3841071D9F6B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{104F16C2-E637-4F59-909B-5D747A959244}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB95DF53E8E6B1AF5DDDDB5B89471D9F742" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63C8EEDE-F0AF-4612-924D-95673371337E}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$129</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$131</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="206">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 374 days</t>
+    <t>OverDue by 381 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -91,7 +91,7 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-09-10)</t>
+    <t>Varies (2025-08-29 → 2026-09-21)</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
@@ -100,10 +100,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 210 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-02-09 → 2026-09-21)</t>
+    <t>OverDue by 217 days</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -112,13 +109,13 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 133 days</t>
+    <t>OverDue by 140 days</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 117 days</t>
+    <t>OverDue by 124 days</t>
   </si>
   <si>
     <t>Varies (2026-05-13 → 2026-09-24)</t>
@@ -130,7 +127,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 84 days</t>
+    <t>OverDue by 91 days</t>
   </si>
   <si>
     <t>Tongfu Microelectronics Co.,Ltd.</t>
@@ -139,67 +136,49 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
-    <t>OverDue by 41 days</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>OverDue by 14 days</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>OverDue by 13 days</t>
+    <t>OverDue by 48 days</t>
+  </si>
+  <si>
+    <t>TI (Philippines) Inc.</t>
+  </si>
+  <si>
+    <t>4516351202_TIPI</t>
+  </si>
+  <si>
+    <t>OverDue by 6 days</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>15 days before Due</t>
+  </si>
+  <si>
+    <t>47383334</t>
+  </si>
+  <si>
+    <t>11 days before Due</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>9 days before Due</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
-    <t>3T/PO262348</t>
-  </si>
-  <si>
-    <t>OverDue by 12 days</t>
-  </si>
-  <si>
-    <t>TI (Philippines) Inc.</t>
-  </si>
-  <si>
-    <t>4516351202_TIPI</t>
-  </si>
-  <si>
-    <t>OverDue by 11 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-08-27 → 2026-09-08)</t>
-  </si>
-  <si>
-    <t>47383334</t>
-  </si>
-  <si>
-    <t>18 days before Due</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>14 days before Due</t>
-  </si>
-  <si>
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>7 days before Due</t>
+    <t>Due Today</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan Limited</t>
@@ -208,166 +187,178 @@
     <t>4516450237</t>
   </si>
   <si>
+    <t>Varies (2026-09-14 → 2026-09-28)</t>
+  </si>
+  <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
   </si>
   <si>
     <t>4516351202_TII</t>
   </si>
   <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>4502615140</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
+    <t>3T/PO262358</t>
   </si>
   <si>
     <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>47375825</t>
-  </si>
-  <si>
-    <t>TBA_ADGT</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC.</t>
-  </si>
-  <si>
-    <t>47369322</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>ARDENTEC CORPORATION</t>
-  </si>
-  <si>
-    <t>4516351202_ARD</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541582747</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
+  </si>
+  <si>
+    <t>4516351202_FFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>3T/PO262348</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>47375825</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC.</t>
+  </si>
+  <si>
+    <t>47369322</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>ARDENTEC CORPORATION</t>
+  </si>
+  <si>
+    <t>4516351202_ARD</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
     <t>8541541216</t>
   </si>
   <si>
@@ -446,15 +437,9 @@
     <t>ES072525</t>
   </si>
   <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
     <t>4516260169</t>
   </si>
   <si>
-    <t>4516446856</t>
-  </si>
-  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -524,6 +509,9 @@
     <t>4020007647</t>
   </si>
   <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
     <t>3030012690</t>
   </si>
   <si>
@@ -551,6 +539,9 @@
     <t>4330007739</t>
   </si>
   <si>
+    <t>4502615140</t>
+  </si>
+  <si>
     <t>FOR TROUBLE SHOOT</t>
   </si>
   <si>
@@ -563,6 +554,12 @@
     <t>BSE-58645</t>
   </si>
   <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
     <t>Texas Instruments CLAB</t>
   </si>
   <si>
@@ -575,12 +572,6 @@
     <t>4516351202_TMX</t>
   </si>
   <si>
-    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
-  </si>
-  <si>
-    <t>4516351202_FFAB</t>
-  </si>
-  <si>
     <t>Texas Instruments FTLABS</t>
   </si>
   <si>
@@ -602,6 +593,12 @@
     <t>4516351202_MIHO-ENG</t>
   </si>
   <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
     <t>Texas Instruments RFAB</t>
   </si>
   <si>
@@ -644,7 +641,7 @@
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>Last updated: 2026-09-07 09:47:50</t>
+    <t>Last updated: 2026-09-14 09:01:43</t>
   </si>
 </sst>
 </file>
@@ -989,12 +986,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1067,7 +1064,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-374</v>
+        <v>-381</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1102,7 +1099,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-374</v>
+        <v>-381</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1137,7 +1134,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-374</v>
+        <v>-381</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1151,28 +1148,28 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="H6">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-374</v>
+        <v>-381</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1189,19 +1186,19 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1210,21 +1207,18 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-210</v>
+        <v>-217</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
       </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -1248,33 +1242,33 @@
         <v>46139</v>
       </c>
       <c r="K8">
-        <v>-133</v>
+        <v>-140</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>53</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1283,21 +1277,21 @@
         <v>46155</v>
       </c>
       <c r="K9">
-        <v>-117</v>
+        <v>-124</v>
       </c>
       <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" t="s">
         <v>31</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1321,18 +1315,18 @@
         <v>46188</v>
       </c>
       <c r="K10">
-        <v>-84</v>
+        <v>-91</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
       </c>
       <c r="C11">
         <v>34</v>
@@ -1356,405 +1350,387 @@
         <v>46231</v>
       </c>
       <c r="K11">
-        <v>-41</v>
+        <v>-48</v>
       </c>
       <c r="L11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12">
+        <v>714</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>691</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46273</v>
+      </c>
+      <c r="K12">
+        <v>-6</v>
+      </c>
+      <c r="L12" t="s">
         <v>40</v>
-      </c>
-      <c r="C12">
-        <v>55</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>54</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46258</v>
-      </c>
-      <c r="K12">
-        <v>-14</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>23</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46294</v>
+      </c>
+      <c r="K13">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
         <v>43</v>
-      </c>
-      <c r="C13">
-        <v>184</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>183</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46259</v>
-      </c>
-      <c r="K13">
-        <v>-13</v>
-      </c>
-      <c r="L13" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46290</v>
+      </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
+      <c r="L14" t="s">
         <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>5</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46260</v>
-      </c>
-      <c r="K14">
-        <v>-12</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46288</v>
+      </c>
+      <c r="K15">
+        <v>9</v>
+      </c>
+      <c r="L15" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15">
-        <v>694</v>
-      </c>
-      <c r="D15">
-        <v>28</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>663</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46261</v>
-      </c>
-      <c r="K15">
-        <v>-11</v>
-      </c>
-      <c r="L15" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>66</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>60</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46279</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
         <v>52</v>
       </c>
-      <c r="C16">
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>4</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>26</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46279</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>22</v>
+      </c>
+      <c r="H18">
+        <v>28</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>46290</v>
-      </c>
-      <c r="K16">
-        <v>18</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="H20">
+        <v>21</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23">
+        <v>54</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>53</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17">
-        <v>22</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="H17">
-        <v>19</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46286</v>
-      </c>
-      <c r="K17">
-        <v>14</v>
-      </c>
-      <c r="L17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18">
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>58</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>46279</v>
-      </c>
-      <c r="K18">
-        <v>7</v>
-      </c>
-      <c r="L18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="H19">
-        <v>26</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>46279</v>
-      </c>
-      <c r="K19">
-        <v>7</v>
-      </c>
-      <c r="L19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20">
-        <v>50</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>22</v>
-      </c>
-      <c r="H20">
-        <v>28</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21">
-        <v>54</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>53</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23">
-        <v>70</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>66</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1766,225 +1742,222 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>70</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>66</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>71</v>
       </c>
-      <c r="C25">
+      <c r="C27">
         <v>19</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27">
+        <v>19</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
         <v>72</v>
       </c>
-      <c r="H25">
-        <v>19</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28">
+        <v>30</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="C26">
-        <v>30</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26">
-        <v>30</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
         <v>74</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
         <v>75</v>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
         <v>76</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" t="s">
-        <v>79</v>
-      </c>
       <c r="C32">
         <v>1</v>
       </c>
@@ -1998,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2009,13 +1982,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2027,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2038,13 +2011,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2056,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2067,13 +2040,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2085,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2096,13 +2069,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2114,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2125,10 +2098,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2143,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2154,13 +2127,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2172,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2183,10 +2156,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2201,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2212,13 +2185,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2230,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H40">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2241,13 +2214,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2259,10 +2232,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2270,13 +2243,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2288,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H42">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2299,13 +2272,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2317,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2328,13 +2301,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2346,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2357,13 +2330,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2375,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2386,10 +2359,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -2404,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -2415,13 +2388,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C47">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2433,10 +2406,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H47">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2444,13 +2417,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2462,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2473,10 +2446,10 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2491,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2502,10 +2475,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2520,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2531,13 +2504,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2549,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2560,13 +2533,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2578,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2589,13 +2562,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C53">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2607,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2618,13 +2591,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2636,10 +2609,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H54">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2647,13 +2620,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2665,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2676,13 +2649,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C56">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2694,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2705,13 +2678,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2723,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2734,13 +2707,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C58">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2752,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H58">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2763,13 +2736,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C59">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2781,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H59">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2792,13 +2765,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C60">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2810,10 +2783,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H60">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2821,13 +2794,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2839,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2850,13 +2823,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2868,10 +2841,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2879,13 +2852,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2897,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H63">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2908,13 +2881,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" t="s">
         <v>113</v>
       </c>
-      <c r="B64" t="s">
-        <v>117</v>
-      </c>
       <c r="C64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2926,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2937,13 +2910,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2955,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2966,10 +2939,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2984,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2995,10 +2968,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3013,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -3024,13 +2997,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3042,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3053,13 +3026,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3071,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3082,13 +3055,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C70">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3100,10 +3073,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H70">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3111,13 +3084,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C71">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3129,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H71">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3140,13 +3113,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3158,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3169,13 +3142,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" t="s">
         <v>126</v>
       </c>
-      <c r="B73" t="s">
-        <v>130</v>
-      </c>
       <c r="C73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3187,10 +3160,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3198,13 +3171,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3216,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H74">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3227,13 +3200,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3245,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3256,13 +3229,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3274,10 +3247,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3285,13 +3258,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3303,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H77">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3314,13 +3287,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C78">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3332,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H78">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3343,13 +3316,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3361,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3372,13 +3345,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C80">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3390,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H80">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3401,13 +3374,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C81">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3419,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H81">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3430,10 +3403,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -3448,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3459,10 +3432,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C83">
         <v>3</v>
@@ -3477,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -3488,10 +3461,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -3506,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3517,10 +3490,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3535,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3546,10 +3519,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B86" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -3564,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H86">
         <v>2</v>
@@ -3575,10 +3548,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3593,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3604,10 +3577,10 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -3622,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H88">
         <v>3</v>
@@ -3633,10 +3606,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -3651,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3662,10 +3635,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3680,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3691,10 +3664,10 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3709,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -3720,10 +3693,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C92">
         <v>5</v>
@@ -3738,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -3749,10 +3722,10 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C93">
         <v>10</v>
@@ -3767,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H93">
         <v>10</v>
@@ -3778,10 +3751,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C94">
         <v>5</v>
@@ -3796,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H94">
         <v>5</v>
@@ -3807,10 +3780,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3825,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -3836,10 +3809,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3854,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3865,10 +3838,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B97" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C97">
         <v>5</v>
@@ -3883,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H97">
         <v>5</v>
@@ -3894,10 +3867,10 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -3912,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H98">
         <v>8</v>
@@ -3923,10 +3896,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C99">
         <v>11</v>
@@ -3941,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H99">
         <v>11</v>
@@ -3952,10 +3925,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C100">
         <v>5</v>
@@ -3970,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H100">
         <v>5</v>
@@ -3981,10 +3954,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B101" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C101">
         <v>21</v>
@@ -3999,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H101">
         <v>21</v>
@@ -4010,10 +3983,10 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -4028,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -4039,10 +4012,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B103" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -4057,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -4068,10 +4041,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B104" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4086,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -4097,10 +4070,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4115,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -4126,10 +4099,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4144,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4155,10 +4128,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4173,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -4184,10 +4157,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4202,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -4213,10 +4186,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B109" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -4231,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H109">
         <v>4</v>
@@ -4242,13 +4215,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4260,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4271,13 +4244,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B111" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4289,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -4300,10 +4273,10 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B112" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -4318,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H112">
         <v>2</v>
@@ -4329,13 +4302,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4347,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4358,13 +4331,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B114" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4376,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4387,13 +4360,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B115" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4405,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H115">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4416,10 +4389,10 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B116" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -4434,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -4445,13 +4418,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4463,10 +4436,10 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4474,10 +4447,10 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B118" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -4492,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H118">
         <v>2</v>
@@ -4503,13 +4476,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B119" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C119">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4521,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H119">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4532,13 +4505,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B120" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4550,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4561,13 +4534,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B121" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C121">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4579,10 +4552,10 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H121">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4590,10 +4563,10 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="B122" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -4608,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H122">
         <v>2</v>
@@ -4619,13 +4592,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B123" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C123">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4637,10 +4610,10 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H123">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -4648,13 +4621,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>198</v>
+        <v>52</v>
       </c>
       <c r="B124" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C124">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -4666,10 +4639,10 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H124">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -4677,13 +4650,13 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="B125" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4695,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -4706,13 +4679,13 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="B126" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4724,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H126">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -4735,10 +4708,10 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c r="B127" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -4753,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -4764,10 +4737,10 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B128" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -4782,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -4793,30 +4766,88 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>70</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A130" t="s">
+        <v>46</v>
+      </c>
+      <c r="B130" t="s">
+        <v>203</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
+        <v>70</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A131" t="s">
+        <v>46</v>
+      </c>
+      <c r="B131" t="s">
+        <v>204</v>
+      </c>
+      <c r="C131">
         <v>5</v>
       </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
-      </c>
-      <c r="F129">
-        <v>0</v>
-      </c>
-      <c r="G129" t="s">
-        <v>72</v>
-      </c>
-      <c r="H129">
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>70</v>
+      </c>
+      <c r="H131">
         <v>5</v>
       </c>
-      <c r="I129">
+      <c r="I131">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB95DF53E8E6B1AF5DDDDB5B89471D9F742" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63C8EEDE-F0AF-4612-924D-95673371337E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9AF25FAC8B9F8E0FE05F3BE6471D9CC94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB5C79C-1E63-4794-849F-61362D6FE9ED}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$131</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$133</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="210">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 381 days</t>
+    <t>OverDue by 398 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -91,7 +91,7 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-09-21)</t>
+    <t>Varies (2025-08-29 → 2026-10-05)</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
@@ -100,7 +100,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 217 days</t>
+    <t>OverDue by 234 days</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -109,16 +109,16 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 140 days</t>
+    <t>OverDue by 157 days</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 124 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-05-13 → 2026-09-24)</t>
+    <t>OverDue by 141 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-10-20)</t>
   </si>
   <si>
     <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
@@ -127,7 +127,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 91 days</t>
+    <t>OverDue by 108 days</t>
   </si>
   <si>
     <t>Tongfu Microelectronics Co.,Ltd.</t>
@@ -136,7 +136,7 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
-    <t>OverDue by 48 days</t>
+    <t>OverDue by 65 days</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -145,6 +145,39 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
+    <t>OverDue by 23 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-09-08 → 2026-10-08)</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>OverDue by 17 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>OverDue by 8 days</t>
+  </si>
+  <si>
+    <t>47383334</t>
+  </si>
+  <si>
     <t>OverDue by 6 days</t>
   </si>
   <si>
@@ -154,40 +187,22 @@
     <t>4516446856</t>
   </si>
   <si>
-    <t>15 days before Due</t>
-  </si>
-  <si>
-    <t>47383334</t>
-  </si>
-  <si>
-    <t>11 days before Due</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>9 days before Due</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>Varies (2026-09-14 → 2026-09-28)</t>
+    <t>14 days before Due</t>
+  </si>
+  <si>
+    <t>3T/PO262358</t>
+  </si>
+  <si>
+    <t>6 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>5 days before Due</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
@@ -196,382 +211,385 @@
     <t>4516351202_TII</t>
   </si>
   <si>
-    <t>3T/PO262358</t>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>47394361</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
   </si>
   <si>
     <t>47301012</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>47375825</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC.</t>
+  </si>
+  <si>
+    <t>47369322</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>ARDENTEC CORPORATION</t>
+  </si>
+  <si>
+    <t>4516351202_ARD</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541541216</t>
+  </si>
+  <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
+    <t>8541563942</t>
+  </si>
+  <si>
+    <t>8541571063</t>
+  </si>
+  <si>
     <t>8541582747</t>
   </si>
   <si>
+    <t>Boston Semi Equipment</t>
+  </si>
+  <si>
+    <t>TBDBSEMY</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBA_BSETH</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment Asia</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>TBD_BSETWN</t>
+  </si>
+  <si>
+    <t>CARDIAC PACEMAKERS INC</t>
+  </si>
+  <si>
+    <t>7000627560</t>
+  </si>
+  <si>
+    <t>7000643410</t>
+  </si>
+  <si>
+    <t>7000667727</t>
+  </si>
+  <si>
+    <t>7000675296</t>
+  </si>
+  <si>
+    <t>7000696372</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
+  </si>
+  <si>
+    <t>4910173913</t>
+  </si>
+  <si>
+    <t>TBD_EVALUATION</t>
+  </si>
+  <si>
+    <t>4910172298</t>
+  </si>
+  <si>
+    <t>JMC Worldwide Inc.</t>
+  </si>
+  <si>
+    <t>ES072525</t>
+  </si>
+  <si>
+    <t>4516260169</t>
+  </si>
+  <si>
+    <t>LPI-2507174</t>
+  </si>
+  <si>
+    <t>Microprecision Calibration Inc.</t>
+  </si>
+  <si>
+    <t>PP25-1057NI</t>
+  </si>
+  <si>
+    <t>PP25-1069NI</t>
+  </si>
+  <si>
+    <t>PP26-1025NI</t>
+  </si>
+  <si>
+    <t>PP26-1051NI</t>
+  </si>
+  <si>
+    <t>3T/PO252272</t>
+  </si>
+  <si>
+    <t>3T/PO252305</t>
+  </si>
+  <si>
+    <t>3T/PO262313</t>
+  </si>
+  <si>
+    <t>3T/PO262321</t>
+  </si>
+  <si>
+    <t>3T/PO262326</t>
+  </si>
+  <si>
+    <t>3T/PO262331</t>
+  </si>
+  <si>
+    <t>3T/PO262333</t>
+  </si>
+  <si>
+    <t>3T/PO262338</t>
+  </si>
+  <si>
+    <t>3T/PO262347</t>
+  </si>
+  <si>
+    <t>3T/PO262348</t>
+  </si>
+  <si>
+    <t>ON Semiconductor Philippines Inc</t>
+  </si>
+  <si>
+    <t>561000005506</t>
+  </si>
+  <si>
+    <t>561000006670</t>
+  </si>
+  <si>
+    <t>Q29327</t>
+  </si>
+  <si>
+    <t>Rhenus Logistics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBDBSETH</t>
+  </si>
+  <si>
+    <t>ST Microelectronics Pte Ltd.</t>
+  </si>
+  <si>
+    <t>4020007186</t>
+  </si>
+  <si>
+    <t>4020007647</t>
+  </si>
+  <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>3030012690</t>
+  </si>
+  <si>
+    <t>4010016033</t>
+  </si>
+  <si>
+    <t>4010016949</t>
+  </si>
+  <si>
+    <t>4010017076</t>
+  </si>
+  <si>
+    <t>4010017128</t>
+  </si>
+  <si>
+    <t>4010017970</t>
+  </si>
+  <si>
+    <t>4010018238</t>
+  </si>
+  <si>
+    <t>4010018600</t>
+  </si>
+  <si>
+    <t>4330007739</t>
+  </si>
+  <si>
+    <t>4502615140</t>
+  </si>
+  <si>
+    <t>FOR TROUBLE SHOOT</t>
+  </si>
+  <si>
+    <t>SWINDON SILICON SYSTEMS</t>
+  </si>
+  <si>
+    <t>23397</t>
+  </si>
+  <si>
+    <t>BSE-58645</t>
+  </si>
+  <si>
+    <t>Texas Instruments CLAB</t>
+  </si>
+  <si>
+    <t>4516351202_CLAB</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DE MEXICO</t>
+  </si>
+  <si>
+    <t>4516351202_TMX</t>
+  </si>
+  <si>
     <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
   </si>
   <si>
     <t>4516351202_FFAB</t>
   </si>
   <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>3T/PO262348</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>47375825</t>
-  </si>
-  <si>
-    <t>TBA_ADGT</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC.</t>
-  </si>
-  <si>
-    <t>47369322</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>ARDENTEC CORPORATION</t>
-  </si>
-  <si>
-    <t>4516351202_ARD</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>8541541216</t>
-  </si>
-  <si>
-    <t>8541550629</t>
-  </si>
-  <si>
-    <t>8541550824</t>
-  </si>
-  <si>
-    <t>8541563942</t>
-  </si>
-  <si>
-    <t>8541571063</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment</t>
-  </si>
-  <si>
-    <t>TBDBSEMY</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>TBA_BSETH</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment Asia</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>TBD_BSETWN</t>
-  </si>
-  <si>
-    <t>CARDIAC PACEMAKERS INC</t>
-  </si>
-  <si>
-    <t>7000627560</t>
-  </si>
-  <si>
-    <t>7000643410</t>
-  </si>
-  <si>
-    <t>7000667727</t>
-  </si>
-  <si>
-    <t>7000675296</t>
-  </si>
-  <si>
-    <t>7000696372</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
-  </si>
-  <si>
-    <t>4910173913</t>
-  </si>
-  <si>
-    <t>TBD_EVALUATION</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>4910172298</t>
-  </si>
-  <si>
-    <t>JMC Worldwide Inc.</t>
-  </si>
-  <si>
-    <t>ES072525</t>
-  </si>
-  <si>
-    <t>4516260169</t>
-  </si>
-  <si>
-    <t>LPI-2507174</t>
-  </si>
-  <si>
-    <t>Microprecision Calibration Inc.</t>
-  </si>
-  <si>
-    <t>PP25-1057NI</t>
-  </si>
-  <si>
-    <t>PP25-1069NI</t>
-  </si>
-  <si>
-    <t>PP26-1025NI</t>
-  </si>
-  <si>
-    <t>PP26-1051NI</t>
-  </si>
-  <si>
-    <t>3T/PO252272</t>
-  </si>
-  <si>
-    <t>3T/PO252305</t>
-  </si>
-  <si>
-    <t>3T/PO262313</t>
-  </si>
-  <si>
-    <t>3T/PO262321</t>
-  </si>
-  <si>
-    <t>3T/PO262326</t>
-  </si>
-  <si>
-    <t>3T/PO262331</t>
-  </si>
-  <si>
-    <t>3T/PO262333</t>
-  </si>
-  <si>
-    <t>3T/PO262338</t>
-  </si>
-  <si>
-    <t>3T/PO262347</t>
-  </si>
-  <si>
-    <t>ON Semiconductor Philippines Inc</t>
-  </si>
-  <si>
-    <t>561000005506</t>
-  </si>
-  <si>
-    <t>561000006670</t>
-  </si>
-  <si>
-    <t>Rhenus Logistics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>TBDBSETH</t>
-  </si>
-  <si>
-    <t>ST Microelectronics Pte Ltd.</t>
-  </si>
-  <si>
-    <t>4020007186</t>
-  </si>
-  <si>
-    <t>4020007647</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>3030012690</t>
-  </si>
-  <si>
-    <t>4010016033</t>
-  </si>
-  <si>
-    <t>4010016949</t>
-  </si>
-  <si>
-    <t>4010017076</t>
-  </si>
-  <si>
-    <t>4010017128</t>
-  </si>
-  <si>
-    <t>4010017970</t>
-  </si>
-  <si>
-    <t>4010018238</t>
-  </si>
-  <si>
-    <t>4010018600</t>
-  </si>
-  <si>
-    <t>4330007739</t>
-  </si>
-  <si>
-    <t>4502615140</t>
-  </si>
-  <si>
-    <t>FOR TROUBLE SHOOT</t>
-  </si>
-  <si>
-    <t>SWINDON SILICON SYSTEMS</t>
-  </si>
-  <si>
-    <t>23397</t>
-  </si>
-  <si>
-    <t>BSE-58645</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>Texas Instruments CLAB</t>
-  </si>
-  <si>
-    <t>4516351202_CLAB</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS DE MEXICO</t>
-  </si>
-  <si>
-    <t>4516351202_TMX</t>
-  </si>
-  <si>
     <t>Texas Instruments FTLABS</t>
   </si>
   <si>
@@ -593,12 +611,6 @@
     <t>4516351202_MIHO-ENG</t>
   </si>
   <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
     <t>Texas Instruments RFAB</t>
   </si>
   <si>
@@ -641,7 +653,7 @@
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>Last updated: 2026-09-14 09:01:43</t>
+    <t>Last updated: 2026-10-01 08:54:41</t>
   </si>
 </sst>
 </file>
@@ -986,12 +998,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M133"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1064,7 +1076,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-381</v>
+        <v>-398</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1099,7 +1111,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-381</v>
+        <v>-398</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1134,7 +1146,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-381</v>
+        <v>-398</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1148,28 +1160,28 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-381</v>
+        <v>-398</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1186,7 +1198,7 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1198,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1207,7 +1219,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-217</v>
+        <v>-234</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
@@ -1227,13 +1239,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1242,7 +1254,7 @@
         <v>46139</v>
       </c>
       <c r="K8">
-        <v>-140</v>
+        <v>-157</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -1256,19 +1268,19 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1277,7 +1289,7 @@
         <v>46155</v>
       </c>
       <c r="K9">
-        <v>-124</v>
+        <v>-141</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
@@ -1315,7 +1327,7 @@
         <v>46188</v>
       </c>
       <c r="K10">
-        <v>-91</v>
+        <v>-108</v>
       </c>
       <c r="L10" t="s">
         <v>34</v>
@@ -1329,7 +1341,7 @@
         <v>36</v>
       </c>
       <c r="C11">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1338,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>33</v>
@@ -1350,7 +1362,7 @@
         <v>46231</v>
       </c>
       <c r="K11">
-        <v>-48</v>
+        <v>-65</v>
       </c>
       <c r="L11" t="s">
         <v>37</v>
@@ -1364,19 +1376,19 @@
         <v>39</v>
       </c>
       <c r="C12">
-        <v>714</v>
+        <v>763</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H12">
-        <v>691</v>
+        <v>734</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1385,94 +1397,97 @@
         <v>46273</v>
       </c>
       <c r="K12">
-        <v>-6</v>
+        <v>-23</v>
       </c>
       <c r="L12" t="s">
         <v>40</v>
       </c>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46294</v>
+        <v>46279</v>
       </c>
       <c r="K13">
-        <v>15</v>
+        <v>-17</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46279</v>
+      </c>
+      <c r="K14">
+        <v>-17</v>
+      </c>
+      <c r="L14" t="s">
         <v>44</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46290</v>
-      </c>
-      <c r="K14">
-        <v>11</v>
-      </c>
-      <c r="L14" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>22</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1481,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1490,48 +1505,48 @@
         <v>46288</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="L15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46279</v>
+        <v>46290</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1539,279 +1554,291 @@
         <v>53</v>
       </c>
       <c r="C17">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46310</v>
+      </c>
+      <c r="K17">
+        <v>14</v>
+      </c>
+      <c r="L17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46302</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="L18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19">
+        <v>199</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>196</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>46301</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="L19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="H20">
+        <v>28</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="H21">
+        <v>25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>57</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>55</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24">
+        <v>54</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>53</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>4</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>26</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46279</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18">
-        <v>50</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>22</v>
-      </c>
-      <c r="H18">
-        <v>28</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>8</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20">
-        <v>25</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
-      <c r="H20">
-        <v>21</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22">
-        <v>9</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>8</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23">
-        <v>54</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>53</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>66</v>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25">
-        <v>70</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>66</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26">
-        <v>5</v>
-      </c>
       <c r="I26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C27">
         <v>19</v>
@@ -1826,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H27">
         <v>19</v>
@@ -1835,12 +1862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1855,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H28">
         <v>30</v>
@@ -1864,12 +1891,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1884,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1893,12 +1920,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1913,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1922,12 +1949,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1942,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1951,12 +1978,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1971,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1985,7 +2012,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2000,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2014,7 +2041,7 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2029,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2043,7 +2070,7 @@
         <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -2058,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H35">
         <v>6</v>
@@ -2072,7 +2099,7 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -2087,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -2101,7 +2128,7 @@
         <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2116,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2130,7 +2157,7 @@
         <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -2145,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H38">
         <v>4</v>
@@ -2159,7 +2186,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2174,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2188,7 +2215,7 @@
         <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2203,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -2217,7 +2244,7 @@
         <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2232,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2246,7 +2273,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C42">
         <v>9</v>
@@ -2261,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H42">
         <v>9</v>
@@ -2275,7 +2302,7 @@
         <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -2290,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H43">
         <v>4</v>
@@ -2304,10 +2331,10 @@
         <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2319,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2333,10 +2360,10 @@
         <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2348,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2362,10 +2389,10 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2377,10 +2404,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2391,7 +2418,7 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -2406,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -2420,10 +2447,10 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2435,10 +2462,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H48">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2449,10 +2476,10 @@
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2464,10 +2491,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2478,7 +2505,7 @@
         <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2493,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2507,7 +2534,7 @@
         <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2522,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2536,10 +2563,10 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2551,10 +2578,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2565,10 +2592,10 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2580,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2594,10 +2621,10 @@
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C54">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2609,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H54">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2623,10 +2650,10 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C55">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2638,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H55">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2652,10 +2679,10 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2667,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2678,13 +2705,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2696,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H57">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2707,13 +2734,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2725,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2736,13 +2763,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C59">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2754,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H59">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2765,13 +2792,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C60">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2783,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H60">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2794,13 +2821,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C61">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2812,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H61">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2823,13 +2850,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2841,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2852,13 +2879,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2870,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2881,13 +2908,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2899,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2910,13 +2937,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2928,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2939,13 +2966,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2957,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2968,10 +2995,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2986,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2997,10 +3024,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3015,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3026,13 +3053,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3044,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3055,10 +3082,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -3073,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3084,13 +3111,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C71">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3102,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H71">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3113,13 +3140,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C72">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3131,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H72">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3142,13 +3169,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3160,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3171,13 +3198,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3189,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3200,13 +3227,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3218,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3232,10 +3259,10 @@
         <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3247,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3261,10 +3288,10 @@
         <v>129</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3276,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3287,13 +3314,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3305,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H78">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3316,13 +3343,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3334,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3345,13 +3372,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3363,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3374,13 +3401,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3392,10 +3419,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H81">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3403,13 +3430,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3421,10 +3448,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3432,13 +3459,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3450,10 +3477,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3461,13 +3488,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B84" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3479,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3490,10 +3517,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3508,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3519,13 +3546,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B86" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3537,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3548,13 +3575,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3566,10 +3593,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3577,13 +3604,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3595,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3606,10 +3633,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -3624,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3635,10 +3662,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3653,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3664,10 +3691,10 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3682,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -3693,13 +3720,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3711,10 +3738,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3722,13 +3749,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C93">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3740,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H93">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3751,13 +3778,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3769,10 +3796,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H94">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3780,10 +3807,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3798,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -3809,13 +3836,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3827,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3838,13 +3865,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3856,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3867,13 +3894,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B98" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3885,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H98">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3899,10 +3926,10 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C99">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3914,10 +3941,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H99">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3928,10 +3955,10 @@
         <v>158</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3943,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3954,13 +3981,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B101" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C101">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3972,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H101">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3983,13 +4010,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B102" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -4001,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4012,13 +4039,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B103" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4030,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4041,13 +4068,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B104" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4059,10 +4086,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4070,10 +4097,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B105" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4088,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -4099,10 +4126,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B106" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4117,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4128,10 +4155,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B107" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4146,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -4157,10 +4184,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B108" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4175,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -4186,13 +4213,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B109" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4204,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4215,13 +4242,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4233,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4244,10 +4271,10 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -4262,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -4273,13 +4300,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B112" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4291,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4302,10 +4329,10 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4320,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H113">
         <v>2</v>
@@ -4331,13 +4358,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C114">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4349,10 +4376,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H114">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4360,13 +4387,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B115" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4378,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4389,13 +4416,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B116" t="s">
         <v>181</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4407,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4436,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -4453,7 +4480,7 @@
         <v>185</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4465,10 +4492,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4476,13 +4503,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4494,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4505,13 +4532,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B120" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C120">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4523,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H120">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4534,13 +4561,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B121" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C121">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4552,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H121">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4563,7 +4590,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B122" t="s">
         <v>192</v>
@@ -4581,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H122">
         <v>2</v>
@@ -4610,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H123">
         <v>9</v>
@@ -4621,10 +4648,10 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="B124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -4639,7 +4666,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H124">
         <v>2</v>
@@ -4650,13 +4677,13 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="B125" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C125">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4668,10 +4695,10 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H125">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -4679,13 +4706,13 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C126">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4697,10 +4724,10 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H126">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -4708,13 +4735,13 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
-        <v>199</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
         <v>200</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4726,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H127">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -4737,13 +4764,13 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="B128" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4755,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -4766,10 +4793,10 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="B129" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -4784,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -4795,10 +4822,10 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B130" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4813,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -4824,30 +4851,88 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B131" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A132" t="s">
+        <v>47</v>
+      </c>
+      <c r="B132" t="s">
+        <v>207</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A133" t="s">
+        <v>47</v>
+      </c>
+      <c r="B133" t="s">
+        <v>208</v>
+      </c>
+      <c r="C133">
         <v>5</v>
       </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-      <c r="F131">
-        <v>0</v>
-      </c>
-      <c r="G131" t="s">
-        <v>70</v>
-      </c>
-      <c r="H131">
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133">
         <v>5</v>
       </c>
-      <c r="I131">
+      <c r="I133">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9AF25FAC8B9F8E0FE05F3BE6471D9CC94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB5C79C-1E63-4794-849F-61362D6FE9ED}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9F0F5F9F5CBF8E0EBAD36879070D9CC69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A66533-8EFB-49BE-97A8-ED585822D7AC}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6053" windowWidth="25600" windowHeight="6914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="211">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 398 days</t>
+    <t>OverDue by 402 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -100,7 +100,10 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 234 days</t>
+    <t>OverDue by 238 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-02-09 → 2026-10-16)</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -109,13 +112,13 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 157 days</t>
+    <t>OverDue by 161 days</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 141 days</t>
+    <t>OverDue by 145 days</t>
   </si>
   <si>
     <t>Varies (2026-05-13 → 2026-10-20)</t>
@@ -127,7 +130,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 108 days</t>
+    <t>OverDue by 112 days</t>
   </si>
   <si>
     <t>Tongfu Microelectronics Co.,Ltd.</t>
@@ -136,7 +139,7 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
-    <t>OverDue by 65 days</t>
+    <t>OverDue by 69 days</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -145,7 +148,7 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 23 days</t>
+    <t>OverDue by 27 days</t>
   </si>
   <si>
     <t>Varies (2026-09-08 → 2026-10-08)</t>
@@ -157,7 +160,10 @@
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>OverDue by 17 days</t>
+    <t>OverDue by 21 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-09-14 → 2026-10-22)</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan Limited</t>
@@ -166,88 +172,85 @@
     <t>4516450237</t>
   </si>
   <si>
+    <t>47383334</t>
+  </si>
+  <si>
+    <t>OverDue by 10 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>11 days before Due</t>
+  </si>
+  <si>
+    <t>3T/PO262358</t>
+  </si>
+  <si>
+    <t>2 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>1 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47394361</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
   </si>
   <si>
     <t>4516351202_UTL</t>
   </si>
   <si>
-    <t>OverDue by 8 days</t>
-  </si>
-  <si>
-    <t>47383334</t>
-  </si>
-  <si>
-    <t>OverDue by 6 days</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>14 days before Due</t>
-  </si>
-  <si>
-    <t>3T/PO262358</t>
-  </si>
-  <si>
-    <t>6 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>5 days before Due</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>47394361</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
     <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
   </si>
   <si>
     <t>47218149</t>
@@ -653,7 +656,7 @@
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>Last updated: 2026-10-01 08:54:41</t>
+    <t>Last updated: 2026-10-05 08:43:11</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1006,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1076,7 +1079,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-398</v>
+        <v>-402</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1111,7 +1114,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-398</v>
+        <v>-402</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1146,7 +1149,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-398</v>
+        <v>-402</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1163,10 +1166,10 @@
         <v>310</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1181,7 +1184,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-398</v>
+        <v>-402</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1201,13 +1204,13 @@
         <v>247</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>235</v>
@@ -1219,18 +1222,21 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-234</v>
+        <v>-238</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
       </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -1254,27 +1260,27 @@
         <v>46139</v>
       </c>
       <c r="K8">
-        <v>-157</v>
+        <v>-161</v>
       </c>
       <c r="L8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>57</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1289,21 +1295,21 @@
         <v>46155</v>
       </c>
       <c r="K9">
-        <v>-141</v>
+        <v>-145</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1327,18 +1333,18 @@
         <v>46188</v>
       </c>
       <c r="K10">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1362,30 +1368,30 @@
         <v>46231</v>
       </c>
       <c r="K11">
-        <v>-65</v>
+        <v>-69</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <v>734</v>
@@ -1397,30 +1403,30 @@
         <v>46273</v>
       </c>
       <c r="K12">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1435,18 +1441,21 @@
         <v>46279</v>
       </c>
       <c r="K13">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="L13" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="M13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -1470,196 +1479,187 @@
         <v>46279</v>
       </c>
       <c r="K14">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="L14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="K15">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46290</v>
+        <v>46311</v>
       </c>
       <c r="K16">
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="L16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46302</v>
+      </c>
+      <c r="K17">
         <v>2</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>24</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46310</v>
-      </c>
-      <c r="K17">
-        <v>14</v>
-      </c>
       <c r="L17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H19">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="I19">
         <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>46301</v>
-      </c>
-      <c r="K19">
-        <v>5</v>
-      </c>
-      <c r="L19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1720,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1731,25 +1731,25 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>70</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>69</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1772,25 +1772,28 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
       </c>
       <c r="H24">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
       <c r="D25">
         <v>0</v>
       </c>
@@ -1800,45 +1803,51 @@
       <c r="F25">
         <v>0</v>
       </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
       <c r="H25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
       <c r="H26">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27">
         <v>19</v>
@@ -1853,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H27">
         <v>19</v>
@@ -1864,10 +1873,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1882,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H28">
         <v>30</v>
@@ -1893,10 +1902,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1911,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1940,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1951,10 +1960,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1969,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1998,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2009,10 +2018,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2027,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2038,10 +2047,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2056,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2067,10 +2076,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -2085,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H35">
         <v>6</v>
@@ -2096,10 +2105,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -2114,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -2125,10 +2134,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2143,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2154,10 +2163,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -2172,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H38">
         <v>4</v>
@@ -2183,10 +2192,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2201,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2212,10 +2221,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2230,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -2241,10 +2250,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2259,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2270,10 +2279,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42">
         <v>9</v>
@@ -2288,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H42">
         <v>9</v>
@@ -2299,10 +2308,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -2317,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H43">
         <v>4</v>
@@ -2328,10 +2337,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44">
         <v>26</v>
@@ -2346,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H44">
         <v>26</v>
@@ -2357,10 +2366,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2375,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -2386,10 +2395,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2404,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2415,10 +2424,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -2433,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -2444,10 +2453,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -2462,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H48">
         <v>4</v>
@@ -2473,10 +2482,10 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49">
         <v>17</v>
@@ -2491,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H49">
         <v>17</v>
@@ -2502,10 +2511,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2520,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2531,10 +2540,10 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2549,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2560,10 +2569,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2578,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2589,10 +2598,10 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -2607,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H53">
         <v>4</v>
@@ -2618,10 +2627,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2636,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -2647,10 +2656,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C55">
         <v>20</v>
@@ -2665,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H55">
         <v>20</v>
@@ -2676,10 +2685,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56">
         <v>13</v>
@@ -2694,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H56">
         <v>13</v>
@@ -2705,10 +2714,10 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2723,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -2734,10 +2743,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -2752,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H58">
         <v>16</v>
@@ -2763,10 +2772,10 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2781,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2792,10 +2801,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C60">
         <v>259</v>
@@ -2810,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H60">
         <v>259</v>
@@ -2821,10 +2830,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C61">
         <v>33</v>
@@ -2839,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H61">
         <v>33</v>
@@ -2850,10 +2859,10 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2868,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H62">
         <v>50</v>
@@ -2879,10 +2888,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2897,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2908,10 +2917,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -2926,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H64">
         <v>2</v>
@@ -2937,10 +2946,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -2955,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H65">
         <v>7</v>
@@ -2966,10 +2975,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -2984,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -2995,10 +3004,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3013,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -3024,10 +3033,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3042,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3053,10 +3062,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3071,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -3082,10 +3091,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -3100,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -3129,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -3140,10 +3149,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3158,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -3169,10 +3178,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C73">
         <v>30</v>
@@ -3187,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H73">
         <v>30</v>
@@ -3198,10 +3207,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C74">
         <v>17</v>
@@ -3216,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H74">
         <v>17</v>
@@ -3227,10 +3236,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3245,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3256,10 +3265,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -3274,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -3285,10 +3294,10 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -3303,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H77">
         <v>10</v>
@@ -3314,10 +3323,10 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C78">
         <v>6</v>
@@ -3332,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H78">
         <v>6</v>
@@ -3343,10 +3352,10 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C79">
         <v>5</v>
@@ -3361,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -3372,10 +3381,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -3390,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H80">
         <v>10</v>
@@ -3401,10 +3410,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -3419,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H81">
         <v>2</v>
@@ -3430,10 +3439,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C82">
         <v>28</v>
@@ -3448,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H82">
         <v>28</v>
@@ -3459,10 +3468,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3477,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3488,10 +3497,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -3506,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -3517,10 +3526,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3535,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3546,10 +3555,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3564,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3575,10 +3584,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -3593,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -3604,10 +3613,10 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -3622,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -3633,10 +3642,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C89">
         <v>3</v>
@@ -3651,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3662,10 +3671,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3680,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3691,10 +3700,10 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3709,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -3720,10 +3729,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -3738,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H92">
         <v>3</v>
@@ -3749,10 +3758,10 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C93">
         <v>5</v>
@@ -3767,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H93">
         <v>5</v>
@@ -3778,10 +3787,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C94">
         <v>10</v>
@@ -3796,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H94">
         <v>10</v>
@@ -3807,10 +3816,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3825,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -3836,10 +3845,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -3854,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H96">
         <v>5</v>
@@ -3865,10 +3874,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C97">
         <v>10</v>
@@ -3883,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H97">
         <v>10</v>
@@ -3894,10 +3903,10 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3912,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3923,10 +3932,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -3941,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H99">
         <v>5</v>
@@ -3952,10 +3961,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B100" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -3970,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3981,10 +3990,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B101" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C101">
         <v>8</v>
@@ -3999,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H101">
         <v>8</v>
@@ -4010,10 +4019,10 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C102">
         <v>11</v>
@@ -4028,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H102">
         <v>11</v>
@@ -4039,10 +4048,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B103" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C103">
         <v>5</v>
@@ -4057,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -4068,10 +4077,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C104">
         <v>21</v>
@@ -4086,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H104">
         <v>21</v>
@@ -4097,10 +4106,10 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -4115,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -4126,10 +4135,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4144,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4155,10 +4164,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B107" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4173,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -4184,10 +4193,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4202,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -4213,10 +4222,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -4231,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -4242,10 +4251,10 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -4260,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -4271,10 +4280,10 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -4289,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -4300,10 +4309,10 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B112" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -4318,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H112">
         <v>4</v>
@@ -4329,10 +4338,10 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B113" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4347,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H113">
         <v>2</v>
@@ -4358,10 +4367,10 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B114" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -4376,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -4387,10 +4396,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -4405,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4416,10 +4425,10 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B116" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4434,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H116">
         <v>2</v>
@@ -4445,10 +4454,10 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B117" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -4463,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -4474,10 +4483,10 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B118" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -4492,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -4503,10 +4512,10 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B119" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C119">
         <v>11</v>
@@ -4521,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H119">
         <v>11</v>
@@ -4532,10 +4541,10 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B120" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -4550,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -4561,10 +4570,10 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B121" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -4579,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H121">
         <v>2</v>
@@ -4590,10 +4599,10 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B122" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -4608,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H122">
         <v>2</v>
@@ -4619,10 +4628,10 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C123">
         <v>9</v>
@@ -4637,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H123">
         <v>9</v>
@@ -4648,10 +4657,10 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -4666,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H124">
         <v>2</v>
@@ -4677,10 +4686,10 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B125" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C125">
         <v>9</v>
@@ -4695,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H125">
         <v>9</v>
@@ -4706,10 +4715,10 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B126" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -4724,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H126">
         <v>2</v>
@@ -4735,10 +4744,10 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B127" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C127">
         <v>24</v>
@@ -4753,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H127">
         <v>24</v>
@@ -4764,10 +4773,10 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B128" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C128">
         <v>170</v>
@@ -4782,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H128">
         <v>170</v>
@@ -4793,10 +4802,10 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B129" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -4811,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -4822,10 +4831,10 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B130" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4840,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -4851,10 +4860,10 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B131" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4869,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -4880,10 +4889,10 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A132" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B132" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4898,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -4909,10 +4918,10 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A133" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B133" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -4927,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H133">
         <v>5</v>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9F0F5F9F5CBF8E0EBAD36879070D9CC69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A66533-8EFB-49BE-97A8-ED585822D7AC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB915453CA25F9AE5136D72A5A071D9C9BF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D2FA168-F3D4-4212-9E4A-2675F9FE98C3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6053" windowWidth="25600" windowHeight="6914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$133</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$135</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="217">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 402 days</t>
+    <t>OverDue by 411 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -100,7 +100,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 238 days</t>
+    <t>OverDue by 247 days</t>
   </si>
   <si>
     <t>Varies (2026-02-09 → 2026-10-16)</t>
@@ -112,16 +112,16 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 161 days</t>
+    <t>OverDue by 170 days</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 145 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-05-13 → 2026-10-20)</t>
+    <t>OverDue by 154 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-10-27)</t>
   </si>
   <si>
     <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
@@ -130,7 +130,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 112 days</t>
+    <t>OverDue by 121 days</t>
   </si>
   <si>
     <t>Tongfu Microelectronics Co.,Ltd.</t>
@@ -139,7 +139,31 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
-    <t>OverDue by 69 days</t>
+    <t>OverDue by 78 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>OverDue by 30 days</t>
+  </si>
+  <si>
+    <t>47383334</t>
+  </si>
+  <si>
+    <t>OverDue by 19 days</t>
+  </si>
+  <si>
+    <t>47400255</t>
+  </si>
+  <si>
+    <t>OverDue by 15 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-09-29 → 2026-10-20)</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -148,58 +172,55 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 27 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-09-08 → 2026-10-08)</t>
+    <t>OverDue by 9 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-10-05 → 2026-10-27)</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>OverDue by 8 days</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
+    <t>3T/PO262358</t>
+  </si>
+  <si>
+    <t>OverDue by 7 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>12 days before Due</t>
+  </si>
+  <si>
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>OverDue by 21 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-09-14 → 2026-10-22)</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>47383334</t>
-  </si>
-  <si>
-    <t>OverDue by 10 days</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>11 days before Due</t>
-  </si>
-  <si>
-    <t>3T/PO262358</t>
-  </si>
-  <si>
-    <t>2 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>1 days before Due</t>
+    <t>8 days before Due</t>
+  </si>
+  <si>
+    <t>Varies (2026-10-22 → 2026-10-29)</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>6 days before Due</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
@@ -208,10 +229,10 @@
     <t>4516351202_TII</t>
   </si>
   <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
   </si>
   <si>
     <t>Texas Instruments LFAB</t>
@@ -220,10 +241,10 @@
     <t>4516351202_LFAB</t>
   </si>
   <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
+  </si>
+  <si>
+    <t>4910173913</t>
   </si>
   <si>
     <t>ROCHESTER ELECTRONICS</t>
@@ -232,109 +253,97 @@
     <t>252395</t>
   </si>
   <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>47375825</t>
+  </si>
+  <si>
     <t>47394361</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>47375825</t>
   </si>
   <si>
     <t>TBA_ADGT</t>
@@ -434,12 +443,6 @@
     <t>7000696372</t>
   </si>
   <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
-  </si>
-  <si>
-    <t>4910173913</t>
-  </si>
-  <si>
     <t>TBD_EVALUATION</t>
   </si>
   <si>
@@ -452,9 +455,15 @@
     <t>ES072525</t>
   </si>
   <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
     <t>4516260169</t>
   </si>
   <si>
+    <t>4516446856</t>
+  </si>
+  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -473,6 +482,9 @@
     <t>PP26-1051NI</t>
   </si>
   <si>
+    <t>PP26-1080NI</t>
+  </si>
+  <si>
     <t>3T/PO252272</t>
   </si>
   <si>
@@ -644,19 +656,25 @@
     <t>4516451338</t>
   </si>
   <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
     <t>43151446</t>
   </si>
   <si>
     <t>43156228</t>
   </si>
   <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
     <t>PO002810</t>
   </si>
   <si>
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>Last updated: 2026-10-05 08:43:11</t>
+    <t>Last updated: 2026-10-14 08:48:48</t>
   </si>
 </sst>
 </file>
@@ -1001,12 +1019,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M133"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1079,7 +1097,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-402</v>
+        <v>-411</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1093,7 +1111,7 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1102,7 +1120,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>352</v>
@@ -1114,7 +1132,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-402</v>
+        <v>-411</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1149,7 +1167,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-402</v>
+        <v>-411</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1163,19 +1181,19 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1184,7 +1202,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-402</v>
+        <v>-411</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1201,19 +1219,19 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1222,7 +1240,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-238</v>
+        <v>-247</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
@@ -1260,7 +1278,7 @@
         <v>46139</v>
       </c>
       <c r="K8">
-        <v>-161</v>
+        <v>-170</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1274,19 +1292,19 @@
         <v>30</v>
       </c>
       <c r="C9">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1295,7 +1313,7 @@
         <v>46155</v>
       </c>
       <c r="K9">
-        <v>-145</v>
+        <v>-154</v>
       </c>
       <c r="L9" t="s">
         <v>31</v>
@@ -1333,7 +1351,7 @@
         <v>46188</v>
       </c>
       <c r="K10">
-        <v>-112</v>
+        <v>-121</v>
       </c>
       <c r="L10" t="s">
         <v>35</v>
@@ -1368,7 +1386,7 @@
         <v>46231</v>
       </c>
       <c r="K11">
-        <v>-69</v>
+        <v>-78</v>
       </c>
       <c r="L11" t="s">
         <v>38</v>
@@ -1382,141 +1400,141 @@
         <v>40</v>
       </c>
       <c r="C12">
-        <v>773</v>
+        <v>30</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>734</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="K12">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="L12" t="s">
         <v>41</v>
       </c>
-      <c r="M12" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46290</v>
+      </c>
+      <c r="K13">
+        <v>-19</v>
+      </c>
+      <c r="L13" t="s">
         <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13">
-        <v>74</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>7</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>62</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46279</v>
-      </c>
-      <c r="K13">
-        <v>-21</v>
-      </c>
-      <c r="L13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C14">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46279</v>
+        <v>46294</v>
       </c>
       <c r="K14">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="L14" t="s">
         <v>45</v>
       </c>
+      <c r="M14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>783</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>16</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>762</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46300</v>
+      </c>
+      <c r="K15">
+        <v>-9</v>
+      </c>
+      <c r="L15" t="s">
         <v>49</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46290</v>
-      </c>
-      <c r="K15">
-        <v>-10</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1528,7 +1546,7 @@
         <v>52</v>
       </c>
       <c r="C16">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1537,39 +1555,39 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46311</v>
+        <v>46301</v>
       </c>
       <c r="K16">
-        <v>11</v>
+        <v>-8</v>
       </c>
       <c r="L16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1584,21 +1602,21 @@
         <v>46302</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1607,56 +1625,68 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46301</v>
+        <v>46321</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>60</v>
       </c>
       <c r="C19">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="J19" s="1">
+        <v>46317</v>
+      </c>
+      <c r="K19">
+        <v>8</v>
+      </c>
+      <c r="L19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>33</v>
@@ -1665,27 +1695,36 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="J20" s="1">
+        <v>46315</v>
+      </c>
+      <c r="K20">
+        <v>6</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1694,24 +1733,24 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1720,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>53</v>
@@ -1729,99 +1768,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25">
         <v>70</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>4</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>66</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A24" t="s">
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25">
-        <v>26</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25">
-        <v>24</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
-        <v>73</v>
-      </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1833,24 +1866,24 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1862,24 +1895,24 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1891,21 +1924,21 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1920,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1929,12 +1962,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1949,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1958,12 +1991,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1978,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1987,12 +2020,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2007,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2021,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2036,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2050,10 +2083,10 @@
         <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2065,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2079,10 +2112,10 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2094,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2108,10 +2141,10 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2123,10 +2156,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2137,10 +2170,10 @@
         <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2152,10 +2185,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2166,10 +2199,10 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2181,10 +2214,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2195,10 +2228,10 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2210,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2224,10 +2257,10 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2239,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2253,10 +2286,10 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2268,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2282,10 +2315,10 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2297,10 +2330,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H42">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2311,10 +2344,10 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2326,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2340,10 +2373,10 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C44">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2355,10 +2388,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H44">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2369,10 +2402,10 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2384,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2398,10 +2431,10 @@
         <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2413,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2427,7 +2460,7 @@
         <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -2442,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -2456,10 +2489,10 @@
         <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2471,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2485,10 +2518,10 @@
         <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2500,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2514,7 +2547,7 @@
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2529,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2543,7 +2576,7 @@
         <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2558,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2572,10 +2605,10 @@
         <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2587,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2601,10 +2634,10 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2616,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2630,10 +2663,10 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2645,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2659,10 +2692,10 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2674,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2688,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C56">
         <v>13</v>
@@ -2703,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H56">
         <v>13</v>
@@ -2717,7 +2750,7 @@
         <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2732,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -2743,10 +2776,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -2761,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H58">
         <v>16</v>
@@ -2772,10 +2805,10 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2790,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2801,10 +2834,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C60">
         <v>259</v>
@@ -2819,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H60">
         <v>259</v>
@@ -2830,10 +2863,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C61">
         <v>33</v>
@@ -2848,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H61">
         <v>33</v>
@@ -2859,10 +2892,10 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -2877,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H62">
         <v>50</v>
@@ -2888,10 +2921,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2906,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2917,10 +2950,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -2935,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H64">
         <v>2</v>
@@ -2946,10 +2979,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -2964,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H65">
         <v>7</v>
@@ -2975,10 +3008,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -2993,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -3004,10 +3037,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3022,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -3033,10 +3066,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3051,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3062,10 +3095,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3080,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -3091,10 +3124,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -3109,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3120,10 +3153,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -3138,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -3149,10 +3182,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3167,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -3178,10 +3211,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C73">
         <v>30</v>
@@ -3196,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H73">
         <v>30</v>
@@ -3207,10 +3240,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C74">
         <v>17</v>
@@ -3225,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H74">
         <v>17</v>
@@ -3236,10 +3269,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3254,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3265,10 +3298,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -3283,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -3294,10 +3327,10 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -3312,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H77">
         <v>10</v>
@@ -3323,13 +3356,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3341,10 +3374,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3352,13 +3385,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3370,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3381,13 +3414,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C80">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3399,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H80">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3410,13 +3443,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B81" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3428,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3439,13 +3472,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C82">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3457,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H82">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3468,10 +3501,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="B83" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3486,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3497,10 +3530,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B84" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -3515,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -3526,10 +3559,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3544,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3555,10 +3588,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3573,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3584,10 +3617,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -3602,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -3613,13 +3646,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3631,10 +3664,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3642,13 +3675,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3660,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3671,10 +3704,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -3689,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3700,10 +3733,10 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3718,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -3729,10 +3762,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -3747,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H92">
         <v>3</v>
@@ -3758,13 +3791,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3776,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3787,13 +3820,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C94">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3805,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H94">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3816,13 +3849,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B95" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3834,10 +3867,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H95">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3845,10 +3878,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B96" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -3863,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H96">
         <v>5</v>
@@ -3874,13 +3907,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3892,10 +3925,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H97">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3903,13 +3936,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3921,10 +3954,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3932,13 +3965,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B99" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3950,10 +3983,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3961,13 +3994,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3979,10 +4012,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3993,10 +4026,10 @@
         <v>163</v>
       </c>
       <c r="B101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -4008,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H101">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4019,13 +4052,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B102" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C102">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -4037,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H102">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4048,13 +4081,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B103" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4066,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H103">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4077,13 +4110,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B104" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C104">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4095,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H104">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4106,13 +4139,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4124,10 +4157,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4135,10 +4168,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4153,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4164,10 +4197,10 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4182,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -4193,10 +4226,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4211,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -4222,10 +4255,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B109" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -4240,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -4251,10 +4284,10 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -4269,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -4280,10 +4313,10 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B111" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -4298,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -4309,13 +4342,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B112" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4327,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4338,13 +4371,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B113" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4356,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4367,13 +4400,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B114" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4385,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4396,13 +4429,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B115" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4414,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4425,10 +4458,10 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B116" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4443,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H116">
         <v>2</v>
@@ -4454,13 +4487,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B117" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4472,10 +4505,10 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4483,10 +4516,10 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -4501,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -4512,13 +4545,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B119" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C119">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4530,10 +4563,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H119">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4541,13 +4574,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B120" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4559,10 +4592,10 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H120">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4570,13 +4603,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B121" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4588,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4599,10 +4632,10 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B122" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -4617,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H122">
         <v>2</v>
@@ -4628,13 +4661,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B123" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C123">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4646,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H123">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -4657,13 +4690,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B124" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -4675,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H124">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -4686,13 +4719,13 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C125">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4704,10 +4737,10 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H125">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -4715,13 +4748,13 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -4733,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H126">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -4744,13 +4777,13 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C127">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4762,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H127">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -4773,13 +4806,13 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
-        <v>202</v>
+        <v>39</v>
       </c>
       <c r="B128" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C128">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4791,10 +4824,10 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H128">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -4802,13 +4835,13 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -4820,10 +4853,10 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -4831,10 +4864,10 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="B130" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4849,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -4860,10 +4893,10 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B131" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4878,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -4889,10 +4922,10 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A132" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B132" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4907,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -4918,30 +4951,88 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A133" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B133" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C133">
+        <v>22</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133">
+        <v>22</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A134" t="s">
+        <v>210</v>
+      </c>
+      <c r="B134" t="s">
+        <v>214</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>77</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A135" t="s">
+        <v>210</v>
+      </c>
+      <c r="B135" t="s">
+        <v>215</v>
+      </c>
+      <c r="C135">
         <v>5</v>
       </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-      <c r="F133">
-        <v>0</v>
-      </c>
-      <c r="G133" t="s">
-        <v>70</v>
-      </c>
-      <c r="H133">
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>77</v>
+      </c>
+      <c r="H135">
         <v>5</v>
       </c>
-      <c r="I133">
+      <c r="I135">
         <v>0</v>
       </c>
     </row>
